--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_arica_y_parinacota.xlsx
@@ -404,7 +404,7 @@
         <v>30.09890318899385</v>
       </c>
       <c r="D2">
-        <v>1.658639690418104</v>
+        <v>3.312194200037799</v>
       </c>
       <c r="E2">
         <v>18.83548369234177</v>
@@ -429,7 +429,7 @@
         <v>32.66666666666666</v>
       </c>
       <c r="D3">
-        <v>1.052631578947368</v>
+        <v>1.60427807486631</v>
       </c>
       <c r="E3">
         <v>31.96581196581197</v>
@@ -454,7 +454,7 @@
         <v>34.07894736842105</v>
       </c>
       <c r="D4">
-        <v>1.340388007054674</v>
+        <v>2.467532467532468</v>
       </c>
       <c r="E4">
         <v>23.21024868123587</v>
@@ -479,7 +479,7 @@
         <v>44.27860696517413</v>
       </c>
       <c r="D5">
-        <v>1.116666666666667</v>
+        <v>2.208791208791209</v>
       </c>
       <c r="E5">
         <v>23.88451443569554</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.09890318899385</v>
+      </c>
+      <c r="C2">
         <v>30.19146642997527</v>
-      </c>
-      <c r="C2">
-        <v>30.09890318899385</v>
       </c>
       <c r="D2">
         <v>3.312194200037799</v>
       </c>
       <c r="E2">
-        <v>18.83548369234177</v>
+        <v>18.77773646697729</v>
       </c>
       <c r="F2">
         <v>62.38677984068094</v>
       </c>
       <c r="G2">
-        <v>18.77773646697729</v>
+        <v>18.83548369234177</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>32.66666666666666</v>
+      </c>
+      <c r="C3">
         <v>62.33333333333333</v>
-      </c>
-      <c r="C3">
-        <v>32.66666666666666</v>
       </c>
       <c r="D3">
         <v>1.60427807486631</v>
       </c>
       <c r="E3">
+        <v>16.75213675213675</v>
+      </c>
+      <c r="F3">
+        <v>51.28205128205128</v>
+      </c>
+      <c r="G3">
         <v>31.96581196581197</v>
-      </c>
-      <c r="F3">
-        <v>51.28205128205129</v>
-      </c>
-      <c r="G3">
-        <v>16.75213675213675</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>34.07894736842105</v>
+      </c>
+      <c r="C4">
         <v>40.52631578947368</v>
-      </c>
-      <c r="C4">
-        <v>34.07894736842105</v>
       </c>
       <c r="D4">
         <v>2.467532467532468</v>
       </c>
       <c r="E4">
-        <v>23.21024868123587</v>
+        <v>19.51770911831198</v>
       </c>
       <c r="F4">
         <v>57.27204220045215</v>
       </c>
       <c r="G4">
-        <v>19.51770911831198</v>
+        <v>23.21024868123587</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>44.27860696517413</v>
+      </c>
+      <c r="C5">
         <v>45.27363184079602</v>
-      </c>
-      <c r="C5">
-        <v>44.27860696517413</v>
       </c>
       <c r="D5">
         <v>2.208791208791209</v>
       </c>
       <c r="E5">
-        <v>23.88451443569554</v>
+        <v>23.35958005249344</v>
       </c>
       <c r="F5">
         <v>52.75590551181102</v>
       </c>
       <c r="G5">
-        <v>23.35958005249344</v>
+        <v>23.88451443569554</v>
       </c>
     </row>
   </sheetData>
